--- a/AAII_Financials/Yearly/BTO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>BTO</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2383200</v>
+        <v>2617500</v>
       </c>
       <c r="E8" s="3">
-        <v>2424000</v>
+        <v>2344500</v>
       </c>
       <c r="F8" s="3">
-        <v>2460700</v>
+        <v>2384700</v>
       </c>
       <c r="G8" s="3">
-        <v>1589600</v>
+        <v>2420800</v>
       </c>
       <c r="H8" s="3">
-        <v>1446200</v>
+        <v>1563800</v>
       </c>
       <c r="I8" s="3">
-        <v>878500</v>
+        <v>1422800</v>
       </c>
       <c r="J8" s="3">
+        <v>864300</v>
+      </c>
+      <c r="K8" s="3">
         <v>939900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>737400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>619900</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1552000</v>
+        <v>1562000</v>
       </c>
       <c r="E9" s="3">
-        <v>1366900</v>
+        <v>1526900</v>
       </c>
       <c r="F9" s="3">
-        <v>1142500</v>
+        <v>1344700</v>
       </c>
       <c r="G9" s="3">
-        <v>970000</v>
+        <v>1124000</v>
       </c>
       <c r="H9" s="3">
-        <v>1576900</v>
+        <v>954200</v>
       </c>
       <c r="I9" s="3">
-        <v>671800</v>
+        <v>1551300</v>
       </c>
       <c r="J9" s="3">
+        <v>660900</v>
+      </c>
+      <c r="K9" s="3">
         <v>650900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>621500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500300</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>831100</v>
+        <v>1055500</v>
       </c>
       <c r="E10" s="3">
-        <v>1057100</v>
+        <v>817700</v>
       </c>
       <c r="F10" s="3">
-        <v>1318100</v>
+        <v>1040000</v>
       </c>
       <c r="G10" s="3">
-        <v>619600</v>
+        <v>1296800</v>
       </c>
       <c r="H10" s="3">
-        <v>-130600</v>
+        <v>609600</v>
       </c>
       <c r="I10" s="3">
-        <v>206700</v>
+        <v>-128500</v>
       </c>
       <c r="J10" s="3">
+        <v>203400</v>
+      </c>
+      <c r="K10" s="3">
         <v>289000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>115900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>119600</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -854,9 +867,12 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,42 +903,48 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15800</v>
+        <v>479300</v>
       </c>
       <c r="E14" s="3">
-        <v>8100</v>
+        <v>15500</v>
       </c>
       <c r="F14" s="3">
-        <v>-220000</v>
+        <v>8000</v>
       </c>
       <c r="G14" s="3">
-        <v>-183400</v>
+        <v>-216500</v>
       </c>
       <c r="H14" s="3">
-        <v>31400</v>
+        <v>-180400</v>
       </c>
       <c r="I14" s="3">
+        <v>30900</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>174200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>972000</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -953,9 +975,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1692100</v>
+        <v>2174400</v>
       </c>
       <c r="E17" s="3">
-        <v>1441000</v>
+        <v>1664700</v>
       </c>
       <c r="F17" s="3">
-        <v>1012400</v>
+        <v>1417700</v>
       </c>
       <c r="G17" s="3">
-        <v>890800</v>
+        <v>995900</v>
       </c>
       <c r="H17" s="3">
-        <v>1052700</v>
+        <v>876400</v>
       </c>
       <c r="I17" s="3">
-        <v>761500</v>
+        <v>1035600</v>
       </c>
       <c r="J17" s="3">
+        <v>749200</v>
+      </c>
+      <c r="K17" s="3">
         <v>756500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>875500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1573300</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>691000</v>
+        <v>443000</v>
       </c>
       <c r="E18" s="3">
-        <v>983000</v>
+        <v>679800</v>
       </c>
       <c r="F18" s="3">
-        <v>1448300</v>
+        <v>967000</v>
       </c>
       <c r="G18" s="3">
-        <v>698800</v>
+        <v>1424800</v>
       </c>
       <c r="H18" s="3">
-        <v>393500</v>
+        <v>687400</v>
       </c>
       <c r="I18" s="3">
-        <v>117000</v>
+        <v>387200</v>
       </c>
       <c r="J18" s="3">
+        <v>115100</v>
+      </c>
+      <c r="K18" s="3">
         <v>183300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-138100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-953400</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>53700</v>
+        <v>9300</v>
       </c>
       <c r="E20" s="3">
-        <v>32200</v>
+        <v>52900</v>
       </c>
       <c r="F20" s="3">
+        <v>31700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
-        <v>16000</v>
-      </c>
       <c r="I20" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-75100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-31500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3500</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1269800</v>
+        <v>994300</v>
       </c>
       <c r="E21" s="3">
-        <v>1533400</v>
+        <v>1249700</v>
       </c>
       <c r="F21" s="3">
-        <v>1857000</v>
+        <v>1509000</v>
       </c>
       <c r="G21" s="3">
-        <v>1043800</v>
+        <v>1827300</v>
       </c>
       <c r="H21" s="3">
-        <v>828700</v>
+        <v>1027200</v>
       </c>
       <c r="I21" s="3">
-        <v>332000</v>
+        <v>815700</v>
       </c>
       <c r="J21" s="3">
+        <v>326800</v>
+      </c>
+      <c r="K21" s="3">
         <v>344000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-806000</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>14900</v>
+        <v>18800</v>
       </c>
       <c r="E22" s="3">
-        <v>16200</v>
+        <v>14700</v>
       </c>
       <c r="F22" s="3">
-        <v>21700</v>
+        <v>16000</v>
       </c>
       <c r="G22" s="3">
-        <v>36500</v>
+        <v>21400</v>
       </c>
       <c r="H22" s="3">
-        <v>42200</v>
+        <v>35900</v>
       </c>
       <c r="I22" s="3">
-        <v>17800</v>
+        <v>41500</v>
       </c>
       <c r="J22" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K22" s="3">
         <v>14000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7300</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>729900</v>
+        <v>433500</v>
       </c>
       <c r="E23" s="3">
-        <v>998900</v>
+        <v>718000</v>
       </c>
       <c r="F23" s="3">
-        <v>1422900</v>
+        <v>982700</v>
       </c>
       <c r="G23" s="3">
-        <v>663500</v>
+        <v>1399800</v>
       </c>
       <c r="H23" s="3">
-        <v>367400</v>
+        <v>652800</v>
       </c>
       <c r="I23" s="3">
-        <v>94800</v>
+        <v>361500</v>
       </c>
       <c r="J23" s="3">
+        <v>93200</v>
+      </c>
+      <c r="K23" s="3">
         <v>94300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-191000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-957200</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>335500</v>
+        <v>377200</v>
       </c>
       <c r="E24" s="3">
-        <v>365100</v>
+        <v>330000</v>
       </c>
       <c r="F24" s="3">
-        <v>498000</v>
+        <v>359100</v>
       </c>
       <c r="G24" s="3">
-        <v>238700</v>
+        <v>489900</v>
       </c>
       <c r="H24" s="3">
-        <v>182100</v>
+        <v>234800</v>
       </c>
       <c r="I24" s="3">
-        <v>10100</v>
+        <v>179100</v>
       </c>
       <c r="J24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K24" s="3">
         <v>41200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-108400</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>394400</v>
+        <v>56300</v>
       </c>
       <c r="E26" s="3">
-        <v>633900</v>
+        <v>388000</v>
       </c>
       <c r="F26" s="3">
-        <v>924900</v>
+        <v>623600</v>
       </c>
       <c r="G26" s="3">
-        <v>424800</v>
+        <v>909900</v>
       </c>
       <c r="H26" s="3">
-        <v>185400</v>
+        <v>417900</v>
       </c>
       <c r="I26" s="3">
-        <v>84700</v>
+        <v>182400</v>
       </c>
       <c r="J26" s="3">
+        <v>83300</v>
+      </c>
+      <c r="K26" s="3">
         <v>53100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-193300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-848800</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>347800</v>
+        <v>13700</v>
       </c>
       <c r="E27" s="3">
-        <v>577800</v>
+        <v>342200</v>
       </c>
       <c r="F27" s="3">
-        <v>863900</v>
+        <v>568400</v>
       </c>
       <c r="G27" s="3">
-        <v>393900</v>
+        <v>849900</v>
       </c>
       <c r="H27" s="3">
-        <v>163100</v>
+        <v>387600</v>
       </c>
       <c r="I27" s="3">
-        <v>78200</v>
+        <v>160500</v>
       </c>
       <c r="J27" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K27" s="3">
         <v>53800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-199700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-847400</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1355,17 +1415,17 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-123300</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+        <v>9400</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-121300</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1376,9 +1436,12 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-53700</v>
+        <v>-9300</v>
       </c>
       <c r="E32" s="3">
-        <v>-32200</v>
+        <v>-52900</v>
       </c>
       <c r="F32" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
-        <v>-16000</v>
-      </c>
       <c r="I32" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>75100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>31500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3500</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>347800</v>
+        <v>13700</v>
       </c>
       <c r="E33" s="3">
-        <v>577800</v>
+        <v>342200</v>
       </c>
       <c r="F33" s="3">
-        <v>863900</v>
+        <v>568400</v>
       </c>
       <c r="G33" s="3">
-        <v>403500</v>
+        <v>849900</v>
       </c>
       <c r="H33" s="3">
-        <v>39800</v>
+        <v>397000</v>
       </c>
       <c r="I33" s="3">
-        <v>78200</v>
+        <v>39200</v>
       </c>
       <c r="J33" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K33" s="3">
         <v>53800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-199700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-847400</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>347800</v>
+        <v>13700</v>
       </c>
       <c r="E35" s="3">
-        <v>577800</v>
+        <v>342200</v>
       </c>
       <c r="F35" s="3">
-        <v>863900</v>
+        <v>568400</v>
       </c>
       <c r="G35" s="3">
-        <v>403500</v>
+        <v>849900</v>
       </c>
       <c r="H35" s="3">
-        <v>39800</v>
+        <v>397000</v>
       </c>
       <c r="I35" s="3">
-        <v>78200</v>
+        <v>39200</v>
       </c>
       <c r="J35" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K35" s="3">
         <v>53800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-199700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-847400</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>896800</v>
+        <v>415300</v>
       </c>
       <c r="E41" s="3">
-        <v>925700</v>
+        <v>882200</v>
       </c>
       <c r="F41" s="3">
-        <v>659800</v>
+        <v>910700</v>
       </c>
       <c r="G41" s="3">
-        <v>193400</v>
+        <v>649100</v>
       </c>
       <c r="H41" s="3">
-        <v>141300</v>
+        <v>190300</v>
       </c>
       <c r="I41" s="3">
-        <v>202800</v>
+        <v>139000</v>
       </c>
       <c r="J41" s="3">
+        <v>199600</v>
+      </c>
+      <c r="K41" s="3">
         <v>199000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>168900</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1708,92 +1797,101 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>40300</v>
+        <v>51000</v>
       </c>
       <c r="E43" s="3">
-        <v>87800</v>
+        <v>39700</v>
       </c>
       <c r="F43" s="3">
-        <v>27200</v>
+        <v>86300</v>
       </c>
       <c r="G43" s="3">
-        <v>67300</v>
+        <v>26700</v>
       </c>
       <c r="H43" s="3">
-        <v>36200</v>
+        <v>66300</v>
       </c>
       <c r="I43" s="3">
-        <v>57700</v>
+        <v>35600</v>
       </c>
       <c r="J43" s="3">
+        <v>56800</v>
+      </c>
+      <c r="K43" s="3">
         <v>38100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39600</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>456700</v>
+        <v>468900</v>
       </c>
       <c r="E44" s="3">
-        <v>374600</v>
+        <v>449300</v>
       </c>
       <c r="F44" s="3">
-        <v>327400</v>
+        <v>368500</v>
       </c>
       <c r="G44" s="3">
-        <v>299800</v>
+        <v>322100</v>
       </c>
       <c r="H44" s="3">
-        <v>321800</v>
+        <v>294900</v>
       </c>
       <c r="I44" s="3">
-        <v>284000</v>
+        <v>316600</v>
       </c>
       <c r="J44" s="3">
+        <v>279400</v>
+      </c>
+      <c r="K44" s="3">
         <v>144000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>115000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122300</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>30100</v>
+        <v>26600</v>
       </c>
       <c r="E45" s="3">
-        <v>50800</v>
+        <v>29600</v>
       </c>
       <c r="F45" s="3">
-        <v>34700</v>
+        <v>50000</v>
       </c>
       <c r="G45" s="3">
-        <v>30300</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+        <v>34100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>29800</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -1807,108 +1905,120 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1423900</v>
+        <v>961800</v>
       </c>
       <c r="E46" s="3">
-        <v>1438900</v>
+        <v>1400800</v>
       </c>
       <c r="F46" s="3">
-        <v>1049100</v>
+        <v>1415600</v>
       </c>
       <c r="G46" s="3">
-        <v>590800</v>
+        <v>1032100</v>
       </c>
       <c r="H46" s="3">
-        <v>499300</v>
+        <v>581200</v>
       </c>
       <c r="I46" s="3">
-        <v>544500</v>
+        <v>491300</v>
       </c>
       <c r="J46" s="3">
+        <v>535700</v>
+      </c>
+      <c r="K46" s="3">
         <v>381100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>271100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>330800</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>382800</v>
+        <v>575800</v>
       </c>
       <c r="E47" s="3">
-        <v>274400</v>
+        <v>376600</v>
       </c>
       <c r="F47" s="3">
-        <v>166400</v>
+        <v>270000</v>
       </c>
       <c r="G47" s="3">
-        <v>223800</v>
+        <v>163700</v>
       </c>
       <c r="H47" s="3">
-        <v>142300</v>
+        <v>220200</v>
       </c>
       <c r="I47" s="3">
-        <v>145300</v>
+        <v>140000</v>
       </c>
       <c r="J47" s="3">
+        <v>142900</v>
+      </c>
+      <c r="K47" s="3">
         <v>122400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>112700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>158200</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3128900</v>
+        <v>4822100</v>
       </c>
       <c r="E48" s="3">
-        <v>3069900</v>
+        <v>3078200</v>
       </c>
       <c r="F48" s="3">
-        <v>3283300</v>
+        <v>3020100</v>
       </c>
       <c r="G48" s="3">
-        <v>2815300</v>
+        <v>3230100</v>
       </c>
       <c r="H48" s="3">
-        <v>2799300</v>
+        <v>2769600</v>
       </c>
       <c r="I48" s="3">
-        <v>2921700</v>
+        <v>2753900</v>
       </c>
       <c r="J48" s="3">
+        <v>2874400</v>
+      </c>
+      <c r="K48" s="3">
         <v>2682700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2295200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2194500</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1939,9 +2049,12 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>127900</v>
+        <v>236600</v>
       </c>
       <c r="E52" s="3">
-        <v>115300</v>
+        <v>125800</v>
       </c>
       <c r="F52" s="3">
-        <v>126100</v>
+        <v>113400</v>
       </c>
       <c r="G52" s="3">
-        <v>60700</v>
+        <v>124100</v>
       </c>
       <c r="H52" s="3">
-        <v>63600</v>
+        <v>59700</v>
       </c>
       <c r="I52" s="3">
-        <v>81900</v>
+        <v>62500</v>
       </c>
       <c r="J52" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K52" s="3">
         <v>27200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15200</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5063500</v>
+        <v>6596300</v>
       </c>
       <c r="E54" s="3">
-        <v>4898600</v>
+        <v>4981400</v>
       </c>
       <c r="F54" s="3">
-        <v>4625000</v>
+        <v>4819100</v>
       </c>
       <c r="G54" s="3">
-        <v>3690600</v>
+        <v>4550000</v>
       </c>
       <c r="H54" s="3">
-        <v>3504500</v>
+        <v>3630700</v>
       </c>
       <c r="I54" s="3">
-        <v>3693400</v>
+        <v>3447700</v>
       </c>
       <c r="J54" s="3">
+        <v>3633600</v>
+      </c>
+      <c r="K54" s="3">
         <v>3213400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2696100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2698700</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,206 +2264,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>157900</v>
+        <v>226100</v>
       </c>
       <c r="E57" s="3">
-        <v>153700</v>
+        <v>155300</v>
       </c>
       <c r="F57" s="3">
-        <v>122500</v>
+        <v>151200</v>
       </c>
       <c r="G57" s="3">
-        <v>114700</v>
+        <v>120500</v>
       </c>
       <c r="H57" s="3">
-        <v>110500</v>
+        <v>112800</v>
       </c>
       <c r="I57" s="3">
-        <v>130800</v>
+        <v>108700</v>
       </c>
       <c r="J57" s="3">
+        <v>128700</v>
+      </c>
+      <c r="K57" s="3">
         <v>112400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67600</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>21300</v>
+        <v>22000</v>
       </c>
       <c r="E58" s="3">
-        <v>34900</v>
+        <v>21000</v>
       </c>
       <c r="F58" s="3">
-        <v>46900</v>
+        <v>34400</v>
       </c>
       <c r="G58" s="3">
-        <v>35800</v>
+        <v>46200</v>
       </c>
       <c r="H58" s="3">
-        <v>34400</v>
+        <v>35200</v>
       </c>
       <c r="I58" s="3">
-        <v>416300</v>
+        <v>33800</v>
       </c>
       <c r="J58" s="3">
+        <v>409500</v>
+      </c>
+      <c r="K58" s="3">
         <v>19200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13300</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>142100</v>
+        <v>176000</v>
       </c>
       <c r="E59" s="3">
-        <v>129400</v>
+        <v>139800</v>
       </c>
       <c r="F59" s="3">
-        <v>224100</v>
+        <v>127300</v>
       </c>
       <c r="G59" s="3">
-        <v>76600</v>
+        <v>220500</v>
       </c>
       <c r="H59" s="3">
-        <v>140200</v>
+        <v>75300</v>
       </c>
       <c r="I59" s="3">
-        <v>133200</v>
+        <v>137900</v>
       </c>
       <c r="J59" s="3">
+        <v>131000</v>
+      </c>
+      <c r="K59" s="3">
         <v>110600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>321300</v>
+        <v>424200</v>
       </c>
       <c r="E60" s="3">
-        <v>318000</v>
+        <v>316100</v>
       </c>
       <c r="F60" s="3">
-        <v>393500</v>
+        <v>312800</v>
       </c>
       <c r="G60" s="3">
-        <v>227000</v>
+        <v>387100</v>
       </c>
       <c r="H60" s="3">
-        <v>285100</v>
+        <v>223400</v>
       </c>
       <c r="I60" s="3">
-        <v>680200</v>
+        <v>280500</v>
       </c>
       <c r="J60" s="3">
+        <v>669200</v>
+      </c>
+      <c r="K60" s="3">
         <v>242100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>131700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>107900</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>57400</v>
+        <v>238000</v>
       </c>
       <c r="E61" s="3">
-        <v>68400</v>
+        <v>56400</v>
       </c>
       <c r="F61" s="3">
-        <v>104400</v>
+        <v>67300</v>
       </c>
       <c r="G61" s="3">
-        <v>324400</v>
+        <v>102700</v>
       </c>
       <c r="H61" s="3">
-        <v>625200</v>
+        <v>319100</v>
       </c>
       <c r="I61" s="3">
-        <v>549600</v>
+        <v>615100</v>
       </c>
       <c r="J61" s="3">
+        <v>540700</v>
+      </c>
+      <c r="K61" s="3">
         <v>650400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>601300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>469800</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>404600</v>
+        <v>643200</v>
       </c>
       <c r="E62" s="3">
-        <v>439300</v>
+        <v>398000</v>
       </c>
       <c r="F62" s="3">
-        <v>467400</v>
+        <v>432200</v>
       </c>
       <c r="G62" s="3">
-        <v>317100</v>
+        <v>459800</v>
       </c>
       <c r="H62" s="3">
-        <v>320700</v>
+        <v>312000</v>
       </c>
       <c r="I62" s="3">
-        <v>309000</v>
+        <v>315500</v>
       </c>
       <c r="J62" s="3">
+        <v>304000</v>
+      </c>
+      <c r="K62" s="3">
         <v>320100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>215000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>172900</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>925900</v>
+        <v>1440100</v>
       </c>
       <c r="E66" s="3">
-        <v>964200</v>
+        <v>910800</v>
       </c>
       <c r="F66" s="3">
-        <v>1087100</v>
+        <v>948600</v>
       </c>
       <c r="G66" s="3">
-        <v>953000</v>
+        <v>1069500</v>
       </c>
       <c r="H66" s="3">
-        <v>1288600</v>
+        <v>937500</v>
       </c>
       <c r="I66" s="3">
-        <v>1558500</v>
+        <v>1267800</v>
       </c>
       <c r="J66" s="3">
+        <v>1533200</v>
+      </c>
+      <c r="K66" s="3">
         <v>1225800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>959800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>826100</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>809000</v>
+        <v>535700</v>
       </c>
       <c r="E72" s="3">
-        <v>697900</v>
+        <v>795900</v>
       </c>
       <c r="F72" s="3">
-        <v>349800</v>
+        <v>686600</v>
       </c>
       <c r="G72" s="3">
-        <v>-359300</v>
+        <v>344200</v>
       </c>
       <c r="H72" s="3">
-        <v>-753600</v>
+        <v>-353500</v>
       </c>
       <c r="I72" s="3">
-        <v>-840300</v>
+        <v>-741300</v>
       </c>
       <c r="J72" s="3">
+        <v>-826700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-918500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-941400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-683500</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4137700</v>
+        <v>5156200</v>
       </c>
       <c r="E76" s="3">
-        <v>3934300</v>
+        <v>4070600</v>
       </c>
       <c r="F76" s="3">
-        <v>3537800</v>
+        <v>3870500</v>
       </c>
       <c r="G76" s="3">
-        <v>2737600</v>
+        <v>3480500</v>
       </c>
       <c r="H76" s="3">
-        <v>2215900</v>
+        <v>2693200</v>
       </c>
       <c r="I76" s="3">
-        <v>2134900</v>
+        <v>2179900</v>
       </c>
       <c r="J76" s="3">
+        <v>2100300</v>
+      </c>
+      <c r="K76" s="3">
         <v>1987600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1736200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1872600</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>347800</v>
+        <v>13700</v>
       </c>
       <c r="E81" s="3">
-        <v>577800</v>
+        <v>342200</v>
       </c>
       <c r="F81" s="3">
-        <v>863900</v>
+        <v>568400</v>
       </c>
       <c r="G81" s="3">
-        <v>403500</v>
+        <v>849900</v>
       </c>
       <c r="H81" s="3">
-        <v>39800</v>
+        <v>397000</v>
       </c>
       <c r="I81" s="3">
-        <v>78200</v>
+        <v>39200</v>
       </c>
       <c r="J81" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K81" s="3">
         <v>53800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-199700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-847400</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>528000</v>
+        <v>544500</v>
       </c>
       <c r="E83" s="3">
-        <v>521200</v>
+        <v>519400</v>
       </c>
       <c r="F83" s="3">
+        <v>512700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>408000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>340100</v>
+      </c>
+      <c r="I83" s="3">
         <v>414700</v>
       </c>
-      <c r="G83" s="3">
-        <v>345700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>421500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>220700</v>
-      </c>
       <c r="J83" s="3">
+        <v>217100</v>
+      </c>
+      <c r="K83" s="3">
         <v>237000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>192200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>143400</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>819500</v>
+        <v>966800</v>
       </c>
       <c r="E89" s="3">
-        <v>996000</v>
+        <v>806200</v>
       </c>
       <c r="F89" s="3">
-        <v>1307600</v>
+        <v>979900</v>
       </c>
       <c r="G89" s="3">
-        <v>676700</v>
+        <v>1286400</v>
       </c>
       <c r="H89" s="3">
-        <v>620200</v>
+        <v>665700</v>
       </c>
       <c r="I89" s="3">
-        <v>213200</v>
+        <v>610100</v>
       </c>
       <c r="J89" s="3">
+        <v>209700</v>
+      </c>
+      <c r="K89" s="3">
         <v>566400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>233600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>149300</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-547500</v>
+        <v>-1097200</v>
       </c>
       <c r="E91" s="3">
-        <v>-415800</v>
+        <v>-538700</v>
       </c>
       <c r="F91" s="3">
-        <v>-485000</v>
+        <v>-409100</v>
       </c>
       <c r="G91" s="3">
-        <v>-359200</v>
+        <v>-477100</v>
       </c>
       <c r="H91" s="3">
-        <v>-373600</v>
+        <v>-353400</v>
       </c>
       <c r="I91" s="3">
-        <v>-586100</v>
+        <v>-367500</v>
       </c>
       <c r="J91" s="3">
+        <v>-576600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-533700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-380700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-611100</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-534800</v>
+        <v>-1143900</v>
       </c>
       <c r="E94" s="3">
-        <v>-393800</v>
+        <v>-526100</v>
       </c>
       <c r="F94" s="3">
-        <v>-464900</v>
+        <v>-387400</v>
       </c>
       <c r="G94" s="3">
-        <v>-367000</v>
+        <v>-457300</v>
       </c>
       <c r="H94" s="3">
-        <v>-376200</v>
+        <v>-361000</v>
       </c>
       <c r="I94" s="3">
-        <v>-477100</v>
+        <v>-370100</v>
       </c>
       <c r="J94" s="3">
+        <v>-469300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-539000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-392800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-369600</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,25 +3521,26 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-234700</v>
+        <v>-252700</v>
       </c>
       <c r="E96" s="3">
-        <v>-231600</v>
+        <v>-230900</v>
       </c>
       <c r="F96" s="3">
-        <v>-158500</v>
+        <v>-227800</v>
       </c>
       <c r="G96" s="3">
-        <v>-14100</v>
+        <v>-156000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-13900</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3321,9 +3554,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-290600</v>
+        <v>-260500</v>
       </c>
       <c r="E100" s="3">
-        <v>-322200</v>
+        <v>-285900</v>
       </c>
       <c r="F100" s="3">
-        <v>-383600</v>
+        <v>-317000</v>
       </c>
       <c r="G100" s="3">
-        <v>-258700</v>
+        <v>-377400</v>
       </c>
       <c r="H100" s="3">
-        <v>-303300</v>
+        <v>-254500</v>
       </c>
       <c r="I100" s="3">
-        <v>265500</v>
+        <v>-298400</v>
       </c>
       <c r="J100" s="3">
+        <v>261200</v>
+      </c>
+      <c r="K100" s="3">
         <v>55700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>71700</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-23100</v>
+        <v>-29300</v>
       </c>
       <c r="E101" s="3">
-        <v>-14200</v>
+        <v>-22700</v>
       </c>
       <c r="F101" s="3">
-        <v>7200</v>
+        <v>-13900</v>
       </c>
       <c r="G101" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4500</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-29000</v>
+        <v>-466900</v>
       </c>
       <c r="E102" s="3">
-        <v>265900</v>
+        <v>-28500</v>
       </c>
       <c r="F102" s="3">
-        <v>466400</v>
+        <v>261600</v>
       </c>
       <c r="G102" s="3">
-        <v>52100</v>
+        <v>458900</v>
       </c>
       <c r="H102" s="3">
-        <v>-61500</v>
+        <v>51200</v>
       </c>
       <c r="I102" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>81900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-63200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-153100</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BTO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BTO_YR_FIN.xlsx
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2617500</v>
+        <v>2654200</v>
       </c>
       <c r="E8" s="3">
-        <v>2344500</v>
+        <v>2377500</v>
       </c>
       <c r="F8" s="3">
-        <v>2384700</v>
+        <v>2418200</v>
       </c>
       <c r="G8" s="3">
-        <v>2420800</v>
+        <v>2454800</v>
       </c>
       <c r="H8" s="3">
-        <v>1563800</v>
+        <v>1585800</v>
       </c>
       <c r="I8" s="3">
-        <v>1422800</v>
+        <v>1442800</v>
       </c>
       <c r="J8" s="3">
-        <v>864300</v>
+        <v>876400</v>
       </c>
       <c r="K8" s="3">
         <v>939900</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1562000</v>
+        <v>1583900</v>
       </c>
       <c r="E9" s="3">
-        <v>1526900</v>
+        <v>1548300</v>
       </c>
       <c r="F9" s="3">
-        <v>1344700</v>
+        <v>1363600</v>
       </c>
       <c r="G9" s="3">
-        <v>1124000</v>
+        <v>1139800</v>
       </c>
       <c r="H9" s="3">
-        <v>954200</v>
+        <v>967600</v>
       </c>
       <c r="I9" s="3">
-        <v>1551300</v>
+        <v>1573100</v>
       </c>
       <c r="J9" s="3">
-        <v>660900</v>
+        <v>670200</v>
       </c>
       <c r="K9" s="3">
         <v>650900</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1055500</v>
+        <v>1070300</v>
       </c>
       <c r="E10" s="3">
-        <v>817700</v>
+        <v>829100</v>
       </c>
       <c r="F10" s="3">
-        <v>1040000</v>
+        <v>1054600</v>
       </c>
       <c r="G10" s="3">
-        <v>1296800</v>
+        <v>1315000</v>
       </c>
       <c r="H10" s="3">
-        <v>609600</v>
+        <v>618100</v>
       </c>
       <c r="I10" s="3">
-        <v>-128500</v>
+        <v>-130300</v>
       </c>
       <c r="J10" s="3">
-        <v>203400</v>
+        <v>206200</v>
       </c>
       <c r="K10" s="3">
         <v>289000</v>
@@ -913,22 +913,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>479300</v>
+        <v>486000</v>
       </c>
       <c r="E14" s="3">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="F14" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G14" s="3">
-        <v>-216500</v>
+        <v>-219500</v>
       </c>
       <c r="H14" s="3">
-        <v>-180400</v>
+        <v>-183000</v>
       </c>
       <c r="I14" s="3">
-        <v>30900</v>
+        <v>31300</v>
       </c>
       <c r="J14" s="3">
         <v>-1100</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2174400</v>
+        <v>2205000</v>
       </c>
       <c r="E17" s="3">
-        <v>1664700</v>
+        <v>1688100</v>
       </c>
       <c r="F17" s="3">
-        <v>1417700</v>
+        <v>1437600</v>
       </c>
       <c r="G17" s="3">
-        <v>995900</v>
+        <v>1009900</v>
       </c>
       <c r="H17" s="3">
-        <v>876400</v>
+        <v>888700</v>
       </c>
       <c r="I17" s="3">
-        <v>1035600</v>
+        <v>1050200</v>
       </c>
       <c r="J17" s="3">
-        <v>749200</v>
+        <v>759700</v>
       </c>
       <c r="K17" s="3">
         <v>756500</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>443000</v>
+        <v>449300</v>
       </c>
       <c r="E18" s="3">
-        <v>679800</v>
+        <v>689400</v>
       </c>
       <c r="F18" s="3">
-        <v>967000</v>
+        <v>980600</v>
       </c>
       <c r="G18" s="3">
-        <v>1424800</v>
+        <v>1444800</v>
       </c>
       <c r="H18" s="3">
-        <v>687400</v>
+        <v>697100</v>
       </c>
       <c r="I18" s="3">
-        <v>387200</v>
+        <v>392600</v>
       </c>
       <c r="J18" s="3">
-        <v>115100</v>
+        <v>116700</v>
       </c>
       <c r="K18" s="3">
         <v>183300</v>
@@ -1086,13 +1086,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="E20" s="3">
-        <v>52900</v>
+        <v>53600</v>
       </c>
       <c r="F20" s="3">
-        <v>31700</v>
+        <v>32100</v>
       </c>
       <c r="G20" s="3">
         <v>-3700</v>
@@ -1101,7 +1101,7 @@
         <v>1300</v>
       </c>
       <c r="I20" s="3">
-        <v>15800</v>
+        <v>16000</v>
       </c>
       <c r="J20" s="3">
         <v>-4400</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>994300</v>
+        <v>1012200</v>
       </c>
       <c r="E21" s="3">
-        <v>1249700</v>
+        <v>1271100</v>
       </c>
       <c r="F21" s="3">
-        <v>1509000</v>
+        <v>1534000</v>
       </c>
       <c r="G21" s="3">
-        <v>1827300</v>
+        <v>1855900</v>
       </c>
       <c r="H21" s="3">
-        <v>1027200</v>
+        <v>1044100</v>
       </c>
       <c r="I21" s="3">
-        <v>815700</v>
+        <v>830200</v>
       </c>
       <c r="J21" s="3">
-        <v>326800</v>
+        <v>333000</v>
       </c>
       <c r="K21" s="3">
         <v>344000</v>
@@ -1158,25 +1158,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="E22" s="3">
-        <v>14700</v>
+        <v>14900</v>
       </c>
       <c r="F22" s="3">
-        <v>16000</v>
+        <v>16200</v>
       </c>
       <c r="G22" s="3">
-        <v>21400</v>
+        <v>21700</v>
       </c>
       <c r="H22" s="3">
-        <v>35900</v>
+        <v>36400</v>
       </c>
       <c r="I22" s="3">
-        <v>41500</v>
+        <v>42100</v>
       </c>
       <c r="J22" s="3">
-        <v>17500</v>
+        <v>17700</v>
       </c>
       <c r="K22" s="3">
         <v>14000</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>433500</v>
+        <v>439600</v>
       </c>
       <c r="E23" s="3">
-        <v>718000</v>
+        <v>728100</v>
       </c>
       <c r="F23" s="3">
-        <v>982700</v>
+        <v>996500</v>
       </c>
       <c r="G23" s="3">
-        <v>1399800</v>
+        <v>1419400</v>
       </c>
       <c r="H23" s="3">
-        <v>652800</v>
+        <v>661900</v>
       </c>
       <c r="I23" s="3">
-        <v>361500</v>
+        <v>366600</v>
       </c>
       <c r="J23" s="3">
-        <v>93200</v>
+        <v>94500</v>
       </c>
       <c r="K23" s="3">
         <v>94300</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>377200</v>
+        <v>382500</v>
       </c>
       <c r="E24" s="3">
-        <v>330000</v>
+        <v>334700</v>
       </c>
       <c r="F24" s="3">
-        <v>359100</v>
+        <v>364200</v>
       </c>
       <c r="G24" s="3">
-        <v>489900</v>
+        <v>496800</v>
       </c>
       <c r="H24" s="3">
-        <v>234800</v>
+        <v>238100</v>
       </c>
       <c r="I24" s="3">
-        <v>179100</v>
+        <v>181600</v>
       </c>
       <c r="J24" s="3">
-        <v>9900</v>
+        <v>10100</v>
       </c>
       <c r="K24" s="3">
         <v>41200</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>56300</v>
+        <v>57100</v>
       </c>
       <c r="E26" s="3">
-        <v>388000</v>
+        <v>393400</v>
       </c>
       <c r="F26" s="3">
-        <v>623600</v>
+        <v>632300</v>
       </c>
       <c r="G26" s="3">
-        <v>909900</v>
+        <v>922700</v>
       </c>
       <c r="H26" s="3">
-        <v>417900</v>
+        <v>423800</v>
       </c>
       <c r="I26" s="3">
-        <v>182400</v>
+        <v>184900</v>
       </c>
       <c r="J26" s="3">
-        <v>83300</v>
+        <v>84500</v>
       </c>
       <c r="K26" s="3">
         <v>53100</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="E27" s="3">
-        <v>342200</v>
+        <v>347000</v>
       </c>
       <c r="F27" s="3">
-        <v>568400</v>
+        <v>576400</v>
       </c>
       <c r="G27" s="3">
-        <v>849900</v>
+        <v>861800</v>
       </c>
       <c r="H27" s="3">
-        <v>387600</v>
+        <v>393000</v>
       </c>
       <c r="I27" s="3">
-        <v>160500</v>
+        <v>162700</v>
       </c>
       <c r="J27" s="3">
-        <v>76900</v>
+        <v>78000</v>
       </c>
       <c r="K27" s="3">
         <v>53800</v>
@@ -1422,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="I29" s="3">
-        <v>-121300</v>
+        <v>-123000</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1518,13 +1518,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-9300</v>
+        <v>-9400</v>
       </c>
       <c r="E32" s="3">
-        <v>-52900</v>
+        <v>-53600</v>
       </c>
       <c r="F32" s="3">
-        <v>-31700</v>
+        <v>-32100</v>
       </c>
       <c r="G32" s="3">
         <v>3700</v>
@@ -1533,7 +1533,7 @@
         <v>-1300</v>
       </c>
       <c r="I32" s="3">
-        <v>-15800</v>
+        <v>-16000</v>
       </c>
       <c r="J32" s="3">
         <v>4400</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="E33" s="3">
-        <v>342200</v>
+        <v>347000</v>
       </c>
       <c r="F33" s="3">
-        <v>568400</v>
+        <v>576400</v>
       </c>
       <c r="G33" s="3">
-        <v>849900</v>
+        <v>861800</v>
       </c>
       <c r="H33" s="3">
-        <v>397000</v>
+        <v>402600</v>
       </c>
       <c r="I33" s="3">
-        <v>39200</v>
+        <v>39700</v>
       </c>
       <c r="J33" s="3">
-        <v>76900</v>
+        <v>78000</v>
       </c>
       <c r="K33" s="3">
         <v>53800</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="E35" s="3">
-        <v>342200</v>
+        <v>347000</v>
       </c>
       <c r="F35" s="3">
-        <v>568400</v>
+        <v>576400</v>
       </c>
       <c r="G35" s="3">
-        <v>849900</v>
+        <v>861800</v>
       </c>
       <c r="H35" s="3">
-        <v>397000</v>
+        <v>402600</v>
       </c>
       <c r="I35" s="3">
-        <v>39200</v>
+        <v>39700</v>
       </c>
       <c r="J35" s="3">
-        <v>76900</v>
+        <v>78000</v>
       </c>
       <c r="K35" s="3">
         <v>53800</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>415300</v>
+        <v>421100</v>
       </c>
       <c r="E41" s="3">
-        <v>882200</v>
+        <v>894600</v>
       </c>
       <c r="F41" s="3">
-        <v>910700</v>
+        <v>923500</v>
       </c>
       <c r="G41" s="3">
-        <v>649100</v>
+        <v>658200</v>
       </c>
       <c r="H41" s="3">
-        <v>190300</v>
+        <v>192900</v>
       </c>
       <c r="I41" s="3">
-        <v>139000</v>
+        <v>141000</v>
       </c>
       <c r="J41" s="3">
-        <v>199600</v>
+        <v>202400</v>
       </c>
       <c r="K41" s="3">
         <v>199000</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>51000</v>
+        <v>51700</v>
       </c>
       <c r="E43" s="3">
-        <v>39700</v>
+        <v>40200</v>
       </c>
       <c r="F43" s="3">
-        <v>86300</v>
+        <v>87500</v>
       </c>
       <c r="G43" s="3">
-        <v>26700</v>
+        <v>27100</v>
       </c>
       <c r="H43" s="3">
-        <v>66300</v>
+        <v>67200</v>
       </c>
       <c r="I43" s="3">
-        <v>35600</v>
+        <v>36100</v>
       </c>
       <c r="J43" s="3">
-        <v>56800</v>
+        <v>57500</v>
       </c>
       <c r="K43" s="3">
         <v>38100</v>
@@ -1843,25 +1843,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>468900</v>
+        <v>475500</v>
       </c>
       <c r="E44" s="3">
-        <v>449300</v>
+        <v>455600</v>
       </c>
       <c r="F44" s="3">
-        <v>368500</v>
+        <v>373700</v>
       </c>
       <c r="G44" s="3">
-        <v>322100</v>
+        <v>326700</v>
       </c>
       <c r="H44" s="3">
-        <v>294900</v>
+        <v>299000</v>
       </c>
       <c r="I44" s="3">
-        <v>316600</v>
+        <v>321100</v>
       </c>
       <c r="J44" s="3">
-        <v>279400</v>
+        <v>283300</v>
       </c>
       <c r="K44" s="3">
         <v>144000</v>
@@ -1879,19 +1879,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="E45" s="3">
-        <v>29600</v>
+        <v>30000</v>
       </c>
       <c r="F45" s="3">
-        <v>50000</v>
+        <v>50700</v>
       </c>
       <c r="G45" s="3">
-        <v>34100</v>
+        <v>34600</v>
       </c>
       <c r="H45" s="3">
-        <v>29800</v>
+        <v>30200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>961800</v>
+        <v>975300</v>
       </c>
       <c r="E46" s="3">
-        <v>1400800</v>
+        <v>1420500</v>
       </c>
       <c r="F46" s="3">
-        <v>1415600</v>
+        <v>1435500</v>
       </c>
       <c r="G46" s="3">
-        <v>1032100</v>
+        <v>1046600</v>
       </c>
       <c r="H46" s="3">
-        <v>581200</v>
+        <v>589400</v>
       </c>
       <c r="I46" s="3">
-        <v>491300</v>
+        <v>498200</v>
       </c>
       <c r="J46" s="3">
-        <v>535700</v>
+        <v>543200</v>
       </c>
       <c r="K46" s="3">
         <v>381100</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>575800</v>
+        <v>583900</v>
       </c>
       <c r="E47" s="3">
-        <v>376600</v>
+        <v>381900</v>
       </c>
       <c r="F47" s="3">
-        <v>270000</v>
+        <v>273800</v>
       </c>
       <c r="G47" s="3">
-        <v>163700</v>
+        <v>166000</v>
       </c>
       <c r="H47" s="3">
-        <v>220200</v>
+        <v>223200</v>
       </c>
       <c r="I47" s="3">
-        <v>140000</v>
+        <v>142000</v>
       </c>
       <c r="J47" s="3">
-        <v>142900</v>
+        <v>144900</v>
       </c>
       <c r="K47" s="3">
         <v>122400</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4822100</v>
+        <v>4889800</v>
       </c>
       <c r="E48" s="3">
-        <v>3078200</v>
+        <v>3121400</v>
       </c>
       <c r="F48" s="3">
-        <v>3020100</v>
+        <v>3062500</v>
       </c>
       <c r="G48" s="3">
-        <v>3230100</v>
+        <v>3275500</v>
       </c>
       <c r="H48" s="3">
-        <v>2769600</v>
+        <v>2808500</v>
       </c>
       <c r="I48" s="3">
-        <v>2753900</v>
+        <v>2792600</v>
       </c>
       <c r="J48" s="3">
-        <v>2874400</v>
+        <v>2914700</v>
       </c>
       <c r="K48" s="3">
         <v>2682700</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>236600</v>
+        <v>240000</v>
       </c>
       <c r="E52" s="3">
+        <v>127600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>115000</v>
+      </c>
+      <c r="G52" s="3">
         <v>125800</v>
       </c>
-      <c r="F52" s="3">
-        <v>113400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>124100</v>
-      </c>
       <c r="H52" s="3">
-        <v>59700</v>
+        <v>60600</v>
       </c>
       <c r="I52" s="3">
-        <v>62500</v>
+        <v>63400</v>
       </c>
       <c r="J52" s="3">
-        <v>80600</v>
+        <v>81700</v>
       </c>
       <c r="K52" s="3">
         <v>27200</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6596300</v>
+        <v>6689000</v>
       </c>
       <c r="E54" s="3">
-        <v>4981400</v>
+        <v>5051400</v>
       </c>
       <c r="F54" s="3">
-        <v>4819100</v>
+        <v>4886800</v>
       </c>
       <c r="G54" s="3">
-        <v>4550000</v>
+        <v>4613900</v>
       </c>
       <c r="H54" s="3">
-        <v>3630700</v>
+        <v>3681700</v>
       </c>
       <c r="I54" s="3">
-        <v>3447700</v>
+        <v>3496100</v>
       </c>
       <c r="J54" s="3">
-        <v>3633600</v>
+        <v>3684600</v>
       </c>
       <c r="K54" s="3">
         <v>3213400</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>226100</v>
+        <v>229300</v>
       </c>
       <c r="E57" s="3">
-        <v>155300</v>
+        <v>157500</v>
       </c>
       <c r="F57" s="3">
-        <v>151200</v>
+        <v>153300</v>
       </c>
       <c r="G57" s="3">
-        <v>120500</v>
+        <v>122200</v>
       </c>
       <c r="H57" s="3">
-        <v>112800</v>
+        <v>114400</v>
       </c>
       <c r="I57" s="3">
-        <v>108700</v>
+        <v>110200</v>
       </c>
       <c r="J57" s="3">
-        <v>128700</v>
+        <v>130500</v>
       </c>
       <c r="K57" s="3">
         <v>112400</v>
@@ -2307,25 +2307,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22000</v>
+        <v>22300</v>
       </c>
       <c r="E58" s="3">
-        <v>21000</v>
+        <v>21300</v>
       </c>
       <c r="F58" s="3">
-        <v>34400</v>
+        <v>34900</v>
       </c>
       <c r="G58" s="3">
-        <v>46200</v>
+        <v>46800</v>
       </c>
       <c r="H58" s="3">
-        <v>35200</v>
+        <v>35700</v>
       </c>
       <c r="I58" s="3">
-        <v>33800</v>
+        <v>34300</v>
       </c>
       <c r="J58" s="3">
-        <v>409500</v>
+        <v>415300</v>
       </c>
       <c r="K58" s="3">
         <v>19200</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>176000</v>
+        <v>178500</v>
       </c>
       <c r="E59" s="3">
-        <v>139800</v>
+        <v>141800</v>
       </c>
       <c r="F59" s="3">
-        <v>127300</v>
+        <v>129100</v>
       </c>
       <c r="G59" s="3">
-        <v>220500</v>
+        <v>223600</v>
       </c>
       <c r="H59" s="3">
-        <v>75300</v>
+        <v>76400</v>
       </c>
       <c r="I59" s="3">
-        <v>137900</v>
+        <v>139900</v>
       </c>
       <c r="J59" s="3">
-        <v>131000</v>
+        <v>132900</v>
       </c>
       <c r="K59" s="3">
         <v>110600</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>424200</v>
+        <v>430100</v>
       </c>
       <c r="E60" s="3">
-        <v>316100</v>
+        <v>320600</v>
       </c>
       <c r="F60" s="3">
-        <v>312800</v>
+        <v>317200</v>
       </c>
       <c r="G60" s="3">
-        <v>387100</v>
+        <v>392600</v>
       </c>
       <c r="H60" s="3">
-        <v>223400</v>
+        <v>226500</v>
       </c>
       <c r="I60" s="3">
-        <v>280500</v>
+        <v>284400</v>
       </c>
       <c r="J60" s="3">
-        <v>669200</v>
+        <v>678600</v>
       </c>
       <c r="K60" s="3">
         <v>242100</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>238000</v>
+        <v>241300</v>
       </c>
       <c r="E61" s="3">
-        <v>56400</v>
+        <v>57200</v>
       </c>
       <c r="F61" s="3">
-        <v>67300</v>
+        <v>68200</v>
       </c>
       <c r="G61" s="3">
-        <v>102700</v>
+        <v>104200</v>
       </c>
       <c r="H61" s="3">
-        <v>319100</v>
+        <v>323600</v>
       </c>
       <c r="I61" s="3">
-        <v>615100</v>
+        <v>623700</v>
       </c>
       <c r="J61" s="3">
-        <v>540700</v>
+        <v>548300</v>
       </c>
       <c r="K61" s="3">
         <v>650400</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>643200</v>
+        <v>652200</v>
       </c>
       <c r="E62" s="3">
-        <v>398000</v>
+        <v>403600</v>
       </c>
       <c r="F62" s="3">
-        <v>432200</v>
+        <v>438200</v>
       </c>
       <c r="G62" s="3">
-        <v>459800</v>
+        <v>466300</v>
       </c>
       <c r="H62" s="3">
-        <v>312000</v>
+        <v>316300</v>
       </c>
       <c r="I62" s="3">
-        <v>315500</v>
+        <v>320000</v>
       </c>
       <c r="J62" s="3">
-        <v>304000</v>
+        <v>308300</v>
       </c>
       <c r="K62" s="3">
         <v>320100</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1440100</v>
+        <v>1460400</v>
       </c>
       <c r="E66" s="3">
-        <v>910800</v>
+        <v>923600</v>
       </c>
       <c r="F66" s="3">
-        <v>948600</v>
+        <v>961900</v>
       </c>
       <c r="G66" s="3">
-        <v>1069500</v>
+        <v>1084500</v>
       </c>
       <c r="H66" s="3">
-        <v>937500</v>
+        <v>950700</v>
       </c>
       <c r="I66" s="3">
-        <v>1267800</v>
+        <v>1285600</v>
       </c>
       <c r="J66" s="3">
-        <v>1533200</v>
+        <v>1554800</v>
       </c>
       <c r="K66" s="3">
         <v>1225800</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>535700</v>
+        <v>543200</v>
       </c>
       <c r="E72" s="3">
-        <v>795900</v>
+        <v>807000</v>
       </c>
       <c r="F72" s="3">
-        <v>686600</v>
+        <v>696200</v>
       </c>
       <c r="G72" s="3">
-        <v>344200</v>
+        <v>349000</v>
       </c>
       <c r="H72" s="3">
-        <v>-353500</v>
+        <v>-358500</v>
       </c>
       <c r="I72" s="3">
-        <v>-741300</v>
+        <v>-751700</v>
       </c>
       <c r="J72" s="3">
-        <v>-826700</v>
+        <v>-838300</v>
       </c>
       <c r="K72" s="3">
         <v>-918500</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5156200</v>
+        <v>5228600</v>
       </c>
       <c r="E76" s="3">
-        <v>4070600</v>
+        <v>4127800</v>
       </c>
       <c r="F76" s="3">
-        <v>3870500</v>
+        <v>3924900</v>
       </c>
       <c r="G76" s="3">
-        <v>3480500</v>
+        <v>3529300</v>
       </c>
       <c r="H76" s="3">
-        <v>2693200</v>
+        <v>2731000</v>
       </c>
       <c r="I76" s="3">
-        <v>2179900</v>
+        <v>2210500</v>
       </c>
       <c r="J76" s="3">
-        <v>2100300</v>
+        <v>2129800</v>
       </c>
       <c r="K76" s="3">
         <v>1987600</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>13700</v>
+        <v>13900</v>
       </c>
       <c r="E81" s="3">
-        <v>342200</v>
+        <v>347000</v>
       </c>
       <c r="F81" s="3">
-        <v>568400</v>
+        <v>576400</v>
       </c>
       <c r="G81" s="3">
-        <v>849900</v>
+        <v>861800</v>
       </c>
       <c r="H81" s="3">
-        <v>397000</v>
+        <v>402600</v>
       </c>
       <c r="I81" s="3">
-        <v>39200</v>
+        <v>39700</v>
       </c>
       <c r="J81" s="3">
-        <v>76900</v>
+        <v>78000</v>
       </c>
       <c r="K81" s="3">
         <v>53800</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>544500</v>
+        <v>552100</v>
       </c>
       <c r="E83" s="3">
-        <v>519400</v>
+        <v>526700</v>
       </c>
       <c r="F83" s="3">
-        <v>512700</v>
+        <v>519900</v>
       </c>
       <c r="G83" s="3">
-        <v>408000</v>
+        <v>413700</v>
       </c>
       <c r="H83" s="3">
-        <v>340100</v>
+        <v>344800</v>
       </c>
       <c r="I83" s="3">
-        <v>414700</v>
+        <v>420500</v>
       </c>
       <c r="J83" s="3">
-        <v>217100</v>
+        <v>220200</v>
       </c>
       <c r="K83" s="3">
         <v>237000</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>966800</v>
+        <v>980400</v>
       </c>
       <c r="E89" s="3">
-        <v>806200</v>
+        <v>817600</v>
       </c>
       <c r="F89" s="3">
-        <v>979900</v>
+        <v>993600</v>
       </c>
       <c r="G89" s="3">
-        <v>1286400</v>
+        <v>1304500</v>
       </c>
       <c r="H89" s="3">
-        <v>665700</v>
+        <v>675100</v>
       </c>
       <c r="I89" s="3">
-        <v>610100</v>
+        <v>618700</v>
       </c>
       <c r="J89" s="3">
-        <v>209700</v>
+        <v>212700</v>
       </c>
       <c r="K89" s="3">
         <v>566400</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1097200</v>
+        <v>-1112600</v>
       </c>
       <c r="E91" s="3">
-        <v>-538700</v>
+        <v>-546200</v>
       </c>
       <c r="F91" s="3">
-        <v>-409100</v>
+        <v>-414800</v>
       </c>
       <c r="G91" s="3">
-        <v>-477100</v>
+        <v>-483800</v>
       </c>
       <c r="H91" s="3">
-        <v>-353400</v>
+        <v>-358400</v>
       </c>
       <c r="I91" s="3">
-        <v>-367500</v>
+        <v>-372700</v>
       </c>
       <c r="J91" s="3">
-        <v>-576600</v>
+        <v>-584700</v>
       </c>
       <c r="K91" s="3">
         <v>-533700</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1143900</v>
+        <v>-1160000</v>
       </c>
       <c r="E94" s="3">
-        <v>-526100</v>
+        <v>-533500</v>
       </c>
       <c r="F94" s="3">
-        <v>-387400</v>
+        <v>-392800</v>
       </c>
       <c r="G94" s="3">
-        <v>-457300</v>
+        <v>-463700</v>
       </c>
       <c r="H94" s="3">
-        <v>-361000</v>
+        <v>-366100</v>
       </c>
       <c r="I94" s="3">
-        <v>-370100</v>
+        <v>-375300</v>
       </c>
       <c r="J94" s="3">
-        <v>-469300</v>
+        <v>-475900</v>
       </c>
       <c r="K94" s="3">
         <v>-539000</v>
@@ -3528,19 +3528,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-252700</v>
+        <v>-256200</v>
       </c>
       <c r="E96" s="3">
-        <v>-230900</v>
+        <v>-234100</v>
       </c>
       <c r="F96" s="3">
-        <v>-227800</v>
+        <v>-231000</v>
       </c>
       <c r="G96" s="3">
-        <v>-156000</v>
+        <v>-158200</v>
       </c>
       <c r="H96" s="3">
-        <v>-13900</v>
+        <v>-14100</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-260500</v>
+        <v>-264200</v>
       </c>
       <c r="E100" s="3">
-        <v>-285900</v>
+        <v>-289900</v>
       </c>
       <c r="F100" s="3">
-        <v>-317000</v>
+        <v>-321400</v>
       </c>
       <c r="G100" s="3">
-        <v>-377400</v>
+        <v>-382700</v>
       </c>
       <c r="H100" s="3">
-        <v>-254500</v>
+        <v>-258100</v>
       </c>
       <c r="I100" s="3">
-        <v>-298400</v>
+        <v>-302600</v>
       </c>
       <c r="J100" s="3">
-        <v>261200</v>
+        <v>264900</v>
       </c>
       <c r="K100" s="3">
         <v>55700</v>
@@ -3708,16 +3708,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-29300</v>
+        <v>-29700</v>
       </c>
       <c r="E101" s="3">
-        <v>-22700</v>
+        <v>-23000</v>
       </c>
       <c r="F101" s="3">
-        <v>-13900</v>
+        <v>-14100</v>
       </c>
       <c r="G101" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="H101" s="3">
         <v>1000</v>
@@ -3744,22 +3744,22 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-466900</v>
+        <v>-473500</v>
       </c>
       <c r="E102" s="3">
-        <v>-28500</v>
+        <v>-28900</v>
       </c>
       <c r="F102" s="3">
-        <v>261600</v>
+        <v>265300</v>
       </c>
       <c r="G102" s="3">
-        <v>458900</v>
+        <v>465300</v>
       </c>
       <c r="H102" s="3">
-        <v>51200</v>
+        <v>51900</v>
       </c>
       <c r="I102" s="3">
-        <v>-60500</v>
+        <v>-61400</v>
       </c>
       <c r="J102" s="3">
         <v>3800</v>
